--- a/data/dividends_info_20261014.xlsx
+++ b/data/dividends_info_20261014.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.15000152587891</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2038505025809472</v>
+        <v>0.2091564084433623</v>
       </c>
       <c r="J2" t="n">
         <v>152</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>61.70000076293945</v>
+        <v>61.45000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.134521866036118</v>
+        <v>1.13913749602778</v>
       </c>
       <c r="J3" t="n">
         <v>131</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.14500045776367</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2038735962549343</v>
+        <v>0.2091564084433623</v>
       </c>
       <c r="J6" t="n">
         <v>61</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.045000076293945</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.765281033120711</v>
+        <v>3.79310350173476</v>
       </c>
       <c r="J7" t="n">
         <v>40</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>52.59999847412109</v>
+        <v>52.20000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6287072425728349</v>
+        <v>0.6335248949551506</v>
       </c>
       <c r="J8" t="n">
         <v>40</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>25.78499984741211</v>
+        <v>25.73500061035156</v>
       </c>
       <c r="I9" t="n">
-        <v>1.047120425044712</v>
+        <v>1.049154822601388</v>
       </c>
       <c r="J9" t="n">
         <v>40</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.38999938964844</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="I10" t="n">
-        <v>2.235695390851087</v>
+        <v>2.257941136430907</v>
       </c>
       <c r="J10" t="n">
         <v>40</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.97999954223633</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.912568385747206</v>
+        <v>1.981132004175294</v>
       </c>
       <c r="J11" t="n">
         <v>33</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.980000019073486</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>3.344481594683792</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J12" t="n">
         <v>33</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.800000190734863</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I13" t="n">
-        <v>1.206896512034959</v>
+        <v>1.228070216532597</v>
       </c>
       <c r="J13" t="n">
         <v>26</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8.029999732971191</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7471980323192279</v>
+        <v>0.7547169992390997</v>
       </c>
       <c r="J14" t="n">
         <v>26</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.75</v>
+        <v>10.56999969482422</v>
       </c>
       <c r="I15" t="n">
-        <v>4.279069767441861</v>
+        <v>4.351939576925881</v>
       </c>
       <c r="J15" t="n">
         <v>12</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.399999618530273</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7142857467236177</v>
+        <v>0.7185628414239557</v>
       </c>
       <c r="J16" t="n">
         <v>5</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7.900000095367432</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4810126524211467</v>
+        <v>0.478589417205906</v>
       </c>
       <c r="J19" t="n">
         <v>-16</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>25.78499984741211</v>
+        <v>25.73500061035156</v>
       </c>
       <c r="I20" t="n">
-        <v>1.047120425044712</v>
+        <v>1.049154822601388</v>
       </c>
       <c r="J20" t="n">
         <v>-23</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.990000009536743</v>
+        <v>1.95799994468689</v>
       </c>
       <c r="I21" t="n">
-        <v>2.864321594313417</v>
+        <v>2.911133892249168</v>
       </c>
       <c r="J21" t="n">
         <v>-23</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>44.14500045776367</v>
+        <v>43.02999877929688</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2038735962549343</v>
+        <v>0.2091564084433623</v>
       </c>
       <c r="J22" t="n">
         <v>-23</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>96.25</v>
+        <v>95.75</v>
       </c>
       <c r="I23" t="n">
-        <v>1.381818181818182</v>
+        <v>1.389033942558747</v>
       </c>
       <c r="J23" t="n">
         <v>-23</v>
@@ -1756,7 +1756,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1766,14 +1766,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1807,7 +1807,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1824,7 +1824,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1834,14 +1834,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1858,7 +1858,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1902,14 +1902,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1936,14 +1936,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1970,14 +1970,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1987,14 +1987,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2191,14 +2191,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2334,7 +2334,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2344,14 +2344,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2361,14 +2361,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2548,14 +2548,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2565,14 +2565,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2633,14 +2633,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2667,14 +2667,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2684,14 +2684,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2769,14 +2769,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2793,12 +2793,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2810,63 +2810,63 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2878,29 +2878,29 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2912,29 +2912,29 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2946,12 +2946,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2980,46 +2980,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3031,58 +3031,58 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3126,14 +3126,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3143,14 +3143,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3184,12 +3184,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3201,12 +3201,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3218,12 +3218,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3235,12 +3235,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3252,12 +3252,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3269,29 +3269,29 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3303,12 +3303,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3320,12 +3320,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3347,14 +3347,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3388,7 +3388,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3415,14 +3415,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3449,14 +3449,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3500,14 +3500,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3592,7 +3592,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3609,7 +3609,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3626,7 +3626,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3660,12 +3660,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3694,12 +3694,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3711,29 +3711,29 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3745,46 +3745,46 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3796,12 +3796,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-11-09</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3813,7 +3813,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3864,7 +3864,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3898,7 +3898,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3908,14 +3908,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3925,14 +3925,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4000,7 +4000,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4010,14 +4010,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4034,7 +4034,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4044,14 +4044,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4068,7 +4068,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4085,7 +4085,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4180,14 +4180,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4204,7 +4204,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4272,7 +4272,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4289,7 +4289,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4306,7 +4306,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4316,14 +4316,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4367,14 +4367,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4408,7 +4408,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4425,7 +4425,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4442,7 +4442,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4459,7 +4459,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4469,14 +4469,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4493,7 +4493,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4503,14 +4503,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4544,7 +4544,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4554,14 +4554,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4571,14 +4571,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4629,7 +4629,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4663,7 +4663,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4680,7 +4680,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4697,7 +4697,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4707,14 +4707,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4724,14 +4724,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4765,7 +4765,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4782,7 +4782,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4884,7 +4884,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4901,7 +4901,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4918,7 +4918,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4969,7 +4969,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4986,7 +4986,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5003,7 +5003,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5064,14 +5064,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5105,7 +5105,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5139,7 +5139,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5190,7 +5190,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5207,7 +5207,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5241,7 +5241,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5258,7 +5258,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5285,14 +5285,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5319,14 +5319,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5360,7 +5360,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5377,7 +5377,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5394,7 +5394,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5411,7 +5411,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5428,7 +5428,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5445,7 +5445,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5462,7 +5462,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5472,14 +5472,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5489,14 +5489,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5513,7 +5513,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5530,7 +5530,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5540,14 +5540,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5564,7 +5564,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5632,7 +5632,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5649,7 +5649,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5700,7 +5700,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5710,14 +5710,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5853,7 +5853,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5863,14 +5863,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5887,7 +5887,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5914,14 +5914,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5938,7 +5938,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5948,14 +5948,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5993,333 +5993,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACEA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CLABO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EUROTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>